--- a/results/q4_output/健康度评价.xlsx
+++ b/results/q4_output/健康度评价.xlsx
@@ -539,7 +539,7 @@
         <v>0.9203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9952</v>
+        <v>0.9993</v>
       </c>
       <c r="H2" t="n">
         <v>0.875</v>
@@ -548,25 +548,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1079</v>
+        <v>0.0219</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1570</v>
+        <v>235.6</v>
       </c>
       <c r="Q2" t="n">
         <v>13885</v>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9941</v>
+        <v>0.9992</v>
       </c>
       <c r="H3" t="n">
         <v>0.8125</v>
@@ -605,25 +605,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="N3" t="n">
-        <v>0.11</v>
+        <v>0.0219</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1771</v>
+        <v>230.8</v>
       </c>
       <c r="Q3" t="n">
         <v>12828</v>
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9943</v>
+        <v>0.9992</v>
       </c>
       <c r="H4" t="n">
         <v>0.0625</v>
@@ -662,25 +662,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7493</v>
+        <v>0.7829</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1272</v>
+        <v>0.0239</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1561.1</v>
+        <v>220.7</v>
       </c>
       <c r="Q4" t="n">
         <v>10805</v>
@@ -710,7 +710,7 @@
         <v>0.9193</v>
       </c>
       <c r="G5" t="n">
-        <v>0.996</v>
+        <v>0.9994</v>
       </c>
       <c r="H5" t="n">
         <v>0.3125</v>
@@ -719,25 +719,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7919</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1128</v>
+        <v>0.0213</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1406.9</v>
+        <v>212.9</v>
       </c>
       <c r="Q5" t="n">
         <v>11954</v>
@@ -767,7 +767,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9937</v>
+        <v>0.999</v>
       </c>
       <c r="H6" t="n">
         <v>0.5625</v>
@@ -776,25 +776,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8197</v>
+        <v>0.8439</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1565</v>
+        <v>0.0289</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1426.4</v>
+        <v>226.5</v>
       </c>
       <c r="Q6" t="n">
         <v>8299</v>
@@ -824,7 +824,7 @@
         <v>0.9466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9948</v>
+        <v>0.9993</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -833,25 +833,25 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6952</v>
+        <v>0.7361</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1234</v>
+        <v>0.0222</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1606.8</v>
+        <v>218.3</v>
       </c>
       <c r="Q7" t="n">
         <v>10391</v>
@@ -881,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="H8" t="n">
         <v>0.625</v>
@@ -890,25 +890,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8996</v>
+        <v>0.9131</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2085</v>
+        <v>0.0312</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1232.4</v>
+        <v>190.4</v>
       </c>
       <c r="Q8" t="n">
         <v>4966</v>
@@ -938,7 +938,7 @@
         <v>0.9353</v>
       </c>
       <c r="G9" t="n">
-        <v>0.997</v>
+        <v>0.9992</v>
       </c>
       <c r="H9" t="n">
         <v>0.6875</v>
@@ -947,25 +947,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8711</v>
+        <v>0.8883</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1199</v>
+        <v>0.0237</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>762.4</v>
+        <v>196.3</v>
       </c>
       <c r="Q9" t="n">
         <v>6437</v>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.994</v>
+        <v>0.9987</v>
       </c>
       <c r="H10" t="n">
         <v>0.1562</v>
@@ -1004,25 +1004,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7743</v>
+        <v>0.8045</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1552</v>
+        <v>0.0346</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>908.2</v>
+        <v>196.3</v>
       </c>
       <c r="Q10" t="n">
         <v>4414</v>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="H11" t="n">
         <v>0.09370000000000001</v>
@@ -1061,25 +1061,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1056</v>
+        <v>0.0246</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>715.4</v>
+        <v>184.1</v>
       </c>
       <c r="Q11" t="n">
         <v>5931</v>
@@ -1109,7 +1109,7 @@
         <v>0.9203</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9947</v>
+        <v>0.9992</v>
       </c>
       <c r="H12" t="n">
         <v>0.875</v>
@@ -1118,25 +1118,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1187</v>
+        <v>0.0241</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1726.9</v>
+        <v>259.1</v>
       </c>
       <c r="Q12" t="n">
         <v>13885</v>
@@ -1166,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9935</v>
+        <v>0.9991</v>
       </c>
       <c r="H13" t="n">
         <v>0.8125</v>
@@ -1175,25 +1175,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="N13" t="n">
-        <v>0.121</v>
+        <v>0.024</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1948.1</v>
+        <v>253.9</v>
       </c>
       <c r="Q13" t="n">
         <v>12828</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9938</v>
+        <v>0.9991</v>
       </c>
       <c r="H14" t="n">
         <v>0.0625</v>
@@ -1232,25 +1232,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7492</v>
+        <v>0.7829</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1399</v>
+        <v>0.0263</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1717.2</v>
+        <v>242.8</v>
       </c>
       <c r="Q14" t="n">
         <v>10805</v>
@@ -1280,7 +1280,7 @@
         <v>0.9193</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9956</v>
+        <v>0.9993</v>
       </c>
       <c r="H15" t="n">
         <v>0.3125</v>
@@ -1289,25 +1289,25 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1241</v>
+        <v>0.0234</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1547.6</v>
+        <v>234.2</v>
       </c>
       <c r="Q15" t="n">
         <v>11954</v>
@@ -1337,7 +1337,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.993</v>
+        <v>0.9989</v>
       </c>
       <c r="H16" t="n">
         <v>0.5625</v>
@@ -1346,25 +1346,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8197</v>
+        <v>0.8439</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1721</v>
+        <v>0.0318</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1569.1</v>
+        <v>249.1</v>
       </c>
       <c r="Q16" t="n">
         <v>8299</v>
@@ -1394,7 +1394,7 @@
         <v>0.9466</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9943</v>
+        <v>0.9992</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1403,25 +1403,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7361</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1358</v>
+        <v>0.0244</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1767.5</v>
+        <v>240.2</v>
       </c>
       <c r="Q17" t="n">
         <v>10391</v>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9927</v>
+        <v>0.9989</v>
       </c>
       <c r="H18" t="n">
         <v>0.625</v>
@@ -1460,25 +1460,25 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8995</v>
+        <v>0.913</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2294</v>
+        <v>0.0343</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1355.6</v>
+        <v>209.4</v>
       </c>
       <c r="Q18" t="n">
         <v>4966</v>
@@ -1508,7 +1508,7 @@
         <v>0.9353</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9967</v>
+        <v>0.9992</v>
       </c>
       <c r="H19" t="n">
         <v>0.6875</v>
@@ -1517,25 +1517,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8711</v>
+        <v>0.8883</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1319</v>
+        <v>0.0261</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>838.6</v>
+        <v>215.9</v>
       </c>
       <c r="Q19" t="n">
         <v>6437</v>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9986</v>
       </c>
       <c r="H20" t="n">
         <v>0.1562</v>
@@ -1574,25 +1574,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7743</v>
+        <v>0.8045</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1707</v>
+        <v>0.038</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>999.1</v>
+        <v>215.9</v>
       </c>
       <c r="Q20" t="n">
         <v>4414</v>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9962</v>
+        <v>0.999</v>
       </c>
       <c r="H21" t="n">
         <v>0.09370000000000001</v>
@@ -1631,25 +1631,25 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1162</v>
+        <v>0.027</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>786.9</v>
+        <v>202.5</v>
       </c>
       <c r="Q21" t="n">
         <v>5931</v>
@@ -1679,7 +1679,7 @@
         <v>0.9203</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9942</v>
+        <v>0.9991</v>
       </c>
       <c r="H22" t="n">
         <v>0.875</v>
@@ -1688,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9448</v>
+        <v>0.9226</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1306</v>
+        <v>0.0265</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1899.6</v>
+        <v>285</v>
       </c>
       <c r="Q22" t="n">
         <v>13885</v>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9796</v>
+        <v>0.9991</v>
       </c>
       <c r="H23" t="n">
         <v>0.8125</v>
@@ -1745,25 +1745,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9617</v>
+        <v>0.9565</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1331</v>
+        <v>0.0264</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2142.9</v>
+        <v>279.3</v>
       </c>
       <c r="Q23" t="n">
         <v>12828</v>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9932</v>
+        <v>0.999</v>
       </c>
       <c r="H24" t="n">
         <v>0.0625</v>
@@ -1802,25 +1802,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8491</v>
+        <v>0.7829</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1539</v>
+        <v>0.0289</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1888.9</v>
+        <v>267.1</v>
       </c>
       <c r="Q24" t="n">
         <v>10805</v>
@@ -1850,7 +1850,7 @@
         <v>0.9193</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9952</v>
+        <v>0.9993</v>
       </c>
       <c r="H25" t="n">
         <v>0.3125</v>
@@ -1859,25 +1859,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M25" t="n">
-        <v>0.856</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1365</v>
+        <v>0.0258</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1702.4</v>
+        <v>257.6</v>
       </c>
       <c r="Q25" t="n">
         <v>11954</v>
@@ -1907,7 +1907,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9923</v>
+        <v>0.9988</v>
       </c>
       <c r="H26" t="n">
         <v>0.5625</v>
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8903</v>
+        <v>0.8439</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1893</v>
+        <v>0.035</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1726</v>
+        <v>274</v>
       </c>
       <c r="Q26" t="n">
         <v>8299</v>
@@ -1964,7 +1964,7 @@
         <v>0.9466</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9937</v>
+        <v>0.9991</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1973,25 +1973,25 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8174</v>
+        <v>0.7361</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1494</v>
+        <v>0.0269</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1944.3</v>
+        <v>264.2</v>
       </c>
       <c r="Q27" t="n">
         <v>10391</v>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.992</v>
+        <v>0.9988</v>
       </c>
       <c r="H28" t="n">
         <v>0.625</v>
@@ -2030,25 +2030,25 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9374</v>
+        <v>0.913</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2523</v>
+        <v>0.0377</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1491.2</v>
+        <v>230.4</v>
       </c>
       <c r="Q28" t="n">
         <v>4966</v>
@@ -2078,7 +2078,7 @@
         <v>0.9353</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9964</v>
+        <v>0.9991</v>
       </c>
       <c r="H29" t="n">
         <v>0.6875</v>
@@ -2087,25 +2087,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9224</v>
+        <v>0.8883</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1451</v>
+        <v>0.0287</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>922.5</v>
+        <v>237.5</v>
       </c>
       <c r="Q29" t="n">
         <v>6437</v>
@@ -2135,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9928</v>
+        <v>0.9984</v>
       </c>
       <c r="H30" t="n">
         <v>0.1562</v>
@@ -2144,25 +2144,25 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8637</v>
+        <v>0.8045</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1878</v>
+        <v>0.0418</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1099</v>
+        <v>237.5</v>
       </c>
       <c r="Q30" t="n">
         <v>4414</v>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9958</v>
+        <v>0.9989</v>
       </c>
       <c r="H31" t="n">
         <v>0.09370000000000001</v>
@@ -2201,25 +2201,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4137</v>
+        <v>0.6065</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4284</v>
+        <v>0.1621</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1578</v>
+        <v>0.2314</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8551</v>
+        <v>0.7901</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1278</v>
+        <v>0.0297</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>865.6</v>
+        <v>222.8</v>
       </c>
       <c r="Q31" t="n">
         <v>5931</v>
@@ -2249,7 +2249,7 @@
         <v>0.9203</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9952</v>
+        <v>0.9993</v>
       </c>
       <c r="H32" t="n">
         <v>0.875</v>
@@ -2258,25 +2258,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1079</v>
+        <v>0.0219</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1570</v>
+        <v>235.6</v>
       </c>
       <c r="Q32" t="n">
         <v>13885</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9941</v>
+        <v>0.9992</v>
       </c>
       <c r="H33" t="n">
         <v>0.8125</v>
@@ -2315,25 +2315,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="N33" t="n">
-        <v>0.11</v>
+        <v>0.0219</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1771</v>
+        <v>230.8</v>
       </c>
       <c r="Q33" t="n">
         <v>12828</v>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9943</v>
+        <v>0.9992</v>
       </c>
       <c r="H34" t="n">
         <v>0.0625</v>
@@ -2372,25 +2372,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7493</v>
+        <v>0.7829</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1272</v>
+        <v>0.0239</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1561.1</v>
+        <v>220.7</v>
       </c>
       <c r="Q34" t="n">
         <v>10805</v>
@@ -2420,7 +2420,7 @@
         <v>0.9193</v>
       </c>
       <c r="G35" t="n">
-        <v>0.996</v>
+        <v>0.9994</v>
       </c>
       <c r="H35" t="n">
         <v>0.3125</v>
@@ -2429,25 +2429,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7919</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1128</v>
+        <v>0.0213</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1406.9</v>
+        <v>212.9</v>
       </c>
       <c r="Q35" t="n">
         <v>11954</v>
@@ -2477,7 +2477,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9937</v>
+        <v>0.999</v>
       </c>
       <c r="H36" t="n">
         <v>0.5625</v>
@@ -2486,25 +2486,25 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8197</v>
+        <v>0.8439</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1565</v>
+        <v>0.0289</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1426.4</v>
+        <v>226.5</v>
       </c>
       <c r="Q36" t="n">
         <v>8299</v>
@@ -2534,7 +2534,7 @@
         <v>0.9466</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9948</v>
+        <v>0.9993</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2543,25 +2543,25 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6952</v>
+        <v>0.7361</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1234</v>
+        <v>0.0222</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1606.8</v>
+        <v>218.3</v>
       </c>
       <c r="Q37" t="n">
         <v>10391</v>
@@ -2591,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="H38" t="n">
         <v>0.625</v>
@@ -2600,25 +2600,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8996</v>
+        <v>0.9131</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2085</v>
+        <v>0.0312</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1232.4</v>
+        <v>190.4</v>
       </c>
       <c r="Q38" t="n">
         <v>4966</v>
@@ -2648,7 +2648,7 @@
         <v>0.9353</v>
       </c>
       <c r="G39" t="n">
-        <v>0.997</v>
+        <v>0.9992</v>
       </c>
       <c r="H39" t="n">
         <v>0.6875</v>
@@ -2657,25 +2657,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8711</v>
+        <v>0.8883</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1199</v>
+        <v>0.0237</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>762.4</v>
+        <v>196.3</v>
       </c>
       <c r="Q39" t="n">
         <v>6437</v>
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.994</v>
+        <v>0.9987</v>
       </c>
       <c r="H40" t="n">
         <v>0.1562</v>
@@ -2714,25 +2714,25 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7743</v>
+        <v>0.8045</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1552</v>
+        <v>0.0346</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>908.2</v>
+        <v>196.3</v>
       </c>
       <c r="Q40" t="n">
         <v>4414</v>
@@ -2762,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="H41" t="n">
         <v>0.09370000000000001</v>
@@ -2771,25 +2771,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1056</v>
+        <v>0.0246</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>715.4</v>
+        <v>184.1</v>
       </c>
       <c r="Q41" t="n">
         <v>5931</v>
@@ -2819,7 +2819,7 @@
         <v>0.9203</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9944</v>
+        <v>0.9992</v>
       </c>
       <c r="H42" t="n">
         <v>0.875</v>
@@ -2828,25 +2828,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1241</v>
+        <v>0.0252</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1805.4</v>
+        <v>270.9</v>
       </c>
       <c r="Q42" t="n">
         <v>13885</v>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9932</v>
+        <v>0.9991</v>
       </c>
       <c r="H43" t="n">
         <v>0.8125</v>
@@ -2885,25 +2885,25 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1265</v>
+        <v>0.0251</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2036.6</v>
+        <v>265.5</v>
       </c>
       <c r="Q43" t="n">
         <v>12828</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9935</v>
+        <v>0.9991</v>
       </c>
       <c r="H44" t="n">
         <v>0.0625</v>
@@ -2942,25 +2942,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7492</v>
+        <v>0.7829</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1462</v>
+        <v>0.0275</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1795.2</v>
+        <v>253.8</v>
       </c>
       <c r="Q44" t="n">
         <v>10805</v>
@@ -2990,7 +2990,7 @@
         <v>0.9193</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9954</v>
+        <v>0.9993</v>
       </c>
       <c r="H45" t="n">
         <v>0.3125</v>
@@ -2999,25 +2999,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1297</v>
+        <v>0.0245</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1618</v>
+        <v>244.9</v>
       </c>
       <c r="Q45" t="n">
         <v>11954</v>
@@ -3047,7 +3047,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9927</v>
+        <v>0.9988</v>
       </c>
       <c r="H46" t="n">
         <v>0.5625</v>
@@ -3056,25 +3056,25 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8197</v>
+        <v>0.8439</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1799</v>
+        <v>0.0332</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1640.4</v>
+        <v>260.5</v>
       </c>
       <c r="Q46" t="n">
         <v>8299</v>
@@ -3104,7 +3104,7 @@
         <v>0.9466</v>
       </c>
       <c r="G47" t="n">
-        <v>0.994</v>
+        <v>0.9992</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3113,25 +3113,25 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7361</v>
       </c>
       <c r="N47" t="n">
-        <v>0.142</v>
+        <v>0.0255</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1847.9</v>
+        <v>251.1</v>
       </c>
       <c r="Q47" t="n">
         <v>10391</v>
@@ -3161,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="H48" t="n">
         <v>0.625</v>
@@ -3170,25 +3170,25 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8995</v>
+        <v>0.913</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2398</v>
+        <v>0.0358</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1417.2</v>
+        <v>218.9</v>
       </c>
       <c r="Q48" t="n">
         <v>4966</v>
@@ -3218,7 +3218,7 @@
         <v>0.9353</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9966</v>
+        <v>0.9991</v>
       </c>
       <c r="H49" t="n">
         <v>0.6875</v>
@@ -3227,25 +3227,25 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M49" t="n">
-        <v>0.871</v>
+        <v>0.8883</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1379</v>
+        <v>0.0273</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>876.7</v>
+        <v>225.7</v>
       </c>
       <c r="Q49" t="n">
         <v>6437</v>
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9931</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>0.1562</v>
@@ -3284,25 +3284,25 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7743</v>
+        <v>0.8045</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1785</v>
+        <v>0.0398</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1044.5</v>
+        <v>225.7</v>
       </c>
       <c r="Q50" t="n">
         <v>4414</v>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.996</v>
+        <v>0.999</v>
       </c>
       <c r="H51" t="n">
         <v>0.09370000000000001</v>
@@ -3341,25 +3341,25 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1215</v>
+        <v>0.0283</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>822.7</v>
+        <v>211.7</v>
       </c>
       <c r="Q51" t="n">
         <v>5931</v>
@@ -3389,7 +3389,7 @@
         <v>0.9203</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9936</v>
+        <v>0.999</v>
       </c>
       <c r="H52" t="n">
         <v>0.875</v>
@@ -3398,25 +3398,25 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9226</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1427</v>
+        <v>0.029</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2076.3</v>
+        <v>311.5</v>
       </c>
       <c r="Q52" t="n">
         <v>13885</v>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8847</v>
+        <v>0.999</v>
       </c>
       <c r="H53" t="n">
         <v>0.8125</v>
@@ -3455,25 +3455,25 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9117</v>
+        <v>0.9564</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1454</v>
+        <v>0.0289</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2342.1</v>
+        <v>305.3</v>
       </c>
       <c r="Q53" t="n">
         <v>12828</v>
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9925</v>
+        <v>0.9989</v>
       </c>
       <c r="H54" t="n">
         <v>0.0625</v>
@@ -3512,25 +3512,25 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8858</v>
+        <v>0.7829</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1682</v>
+        <v>0.0316</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2064.5</v>
+        <v>291.9</v>
       </c>
       <c r="Q54" t="n">
         <v>10805</v>
@@ -3560,7 +3560,7 @@
         <v>0.9193</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9947</v>
+        <v>0.9992</v>
       </c>
       <c r="H55" t="n">
         <v>0.3125</v>
@@ -3569,25 +3569,25 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1492</v>
+        <v>0.0282</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1860.6</v>
+        <v>281.6</v>
       </c>
       <c r="Q55" t="n">
         <v>11954</v>
@@ -3617,7 +3617,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9916</v>
+        <v>0.9987</v>
       </c>
       <c r="H56" t="n">
         <v>0.5625</v>
@@ -3626,25 +3626,25 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M56" t="n">
-        <v>0.9162</v>
+        <v>0.8438</v>
       </c>
       <c r="N56" t="n">
-        <v>0.2069</v>
+        <v>0.0382</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1886.5</v>
+        <v>299.5</v>
       </c>
       <c r="Q56" t="n">
         <v>8299</v>
@@ -3674,7 +3674,7 @@
         <v>0.9466</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9881</v>
+        <v>0.9991</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3683,25 +3683,25 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8595</v>
+        <v>0.736</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1633</v>
+        <v>0.0294</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2125</v>
+        <v>288.8</v>
       </c>
       <c r="Q57" t="n">
         <v>10391</v>
@@ -3731,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9912</v>
+        <v>0.9986</v>
       </c>
       <c r="H58" t="n">
         <v>0.625</v>
@@ -3740,25 +3740,25 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M58" t="n">
-        <v>0.951</v>
+        <v>0.913</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2758</v>
+        <v>0.0412</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1629.8</v>
+        <v>251.8</v>
       </c>
       <c r="Q58" t="n">
         <v>4966</v>
@@ -3788,7 +3788,7 @@
         <v>0.9353</v>
       </c>
       <c r="G59" t="n">
-        <v>0.996</v>
+        <v>0.999</v>
       </c>
       <c r="H59" t="n">
         <v>0.6875</v>
@@ -3797,25 +3797,25 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9412</v>
+        <v>0.8883</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1586</v>
+        <v>0.0314</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1008.2</v>
+        <v>259.6</v>
       </c>
       <c r="Q59" t="n">
         <v>6437</v>
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9921</v>
+        <v>0.9983</v>
       </c>
       <c r="H60" t="n">
         <v>0.1562</v>
@@ -3854,25 +3854,25 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8966</v>
+        <v>0.8045</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2052</v>
+        <v>0.0457</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1201.2</v>
+        <v>259.6</v>
       </c>
       <c r="Q60" t="n">
         <v>4414</v>
@@ -3902,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9954</v>
+        <v>0.9988</v>
       </c>
       <c r="H61" t="n">
         <v>0.09370000000000001</v>
@@ -3911,25 +3911,25 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3072</v>
+        <v>0.6065</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5756</v>
+        <v>0.1621</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1172</v>
+        <v>0.2314</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8911</v>
+        <v>0.7901</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1397</v>
+        <v>0.0325</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>946.1</v>
+        <v>243.5</v>
       </c>
       <c r="Q61" t="n">
         <v>5931</v>
@@ -3959,7 +3959,7 @@
         <v>0.9203</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9952</v>
+        <v>0.9993</v>
       </c>
       <c r="H62" t="n">
         <v>0.875</v>
@@ -3968,25 +3968,25 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1079</v>
+        <v>0.0219</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1570</v>
+        <v>235.6</v>
       </c>
       <c r="Q62" t="n">
         <v>13885</v>
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9941</v>
+        <v>0.9992</v>
       </c>
       <c r="H63" t="n">
         <v>0.8125</v>
@@ -4025,25 +4025,25 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="N63" t="n">
-        <v>0.11</v>
+        <v>0.0219</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1771</v>
+        <v>230.8</v>
       </c>
       <c r="Q63" t="n">
         <v>12828</v>
@@ -4073,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9943</v>
+        <v>0.9992</v>
       </c>
       <c r="H64" t="n">
         <v>0.0625</v>
@@ -4082,25 +4082,25 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7493</v>
+        <v>0.7829</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1272</v>
+        <v>0.0239</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1561.1</v>
+        <v>220.7</v>
       </c>
       <c r="Q64" t="n">
         <v>10805</v>
@@ -4130,7 +4130,7 @@
         <v>0.9193</v>
       </c>
       <c r="G65" t="n">
-        <v>0.996</v>
+        <v>0.9994</v>
       </c>
       <c r="H65" t="n">
         <v>0.3125</v>
@@ -4139,25 +4139,25 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7919</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1128</v>
+        <v>0.0213</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1406.9</v>
+        <v>212.9</v>
       </c>
       <c r="Q65" t="n">
         <v>11954</v>
@@ -4187,7 +4187,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9937</v>
+        <v>0.999</v>
       </c>
       <c r="H66" t="n">
         <v>0.5625</v>
@@ -4196,25 +4196,25 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8197</v>
+        <v>0.8439</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1565</v>
+        <v>0.0289</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1426.4</v>
+        <v>226.5</v>
       </c>
       <c r="Q66" t="n">
         <v>8299</v>
@@ -4244,7 +4244,7 @@
         <v>0.9466</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9948</v>
+        <v>0.9993</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -4253,25 +4253,25 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6952</v>
+        <v>0.7361</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1234</v>
+        <v>0.0222</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1606.8</v>
+        <v>218.3</v>
       </c>
       <c r="Q67" t="n">
         <v>10391</v>
@@ -4301,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="H68" t="n">
         <v>0.625</v>
@@ -4310,25 +4310,25 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8996</v>
+        <v>0.9131</v>
       </c>
       <c r="N68" t="n">
-        <v>0.2085</v>
+        <v>0.0312</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1232.4</v>
+        <v>190.4</v>
       </c>
       <c r="Q68" t="n">
         <v>4966</v>
@@ -4358,7 +4358,7 @@
         <v>0.9353</v>
       </c>
       <c r="G69" t="n">
-        <v>0.997</v>
+        <v>0.9992</v>
       </c>
       <c r="H69" t="n">
         <v>0.6875</v>
@@ -4367,25 +4367,25 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8711</v>
+        <v>0.8883</v>
       </c>
       <c r="N69" t="n">
-        <v>0.1199</v>
+        <v>0.0237</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>762.4</v>
+        <v>196.3</v>
       </c>
       <c r="Q69" t="n">
         <v>6437</v>
@@ -4415,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.994</v>
+        <v>0.9987</v>
       </c>
       <c r="H70" t="n">
         <v>0.1562</v>
@@ -4424,25 +4424,25 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7743</v>
+        <v>0.8045</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1552</v>
+        <v>0.0346</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>908.2</v>
+        <v>196.3</v>
       </c>
       <c r="Q70" t="n">
         <v>4414</v>
@@ -4472,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="H71" t="n">
         <v>0.09370000000000001</v>
@@ -4481,25 +4481,25 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0.7005</v>
+        <v>0.6065</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0322</v>
+        <v>0.1621</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2673</v>
+        <v>0.2314</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1056</v>
+        <v>0.0246</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>715.4</v>
+        <v>184.1</v>
       </c>
       <c r="Q71" t="n">
         <v>5931</v>
@@ -4529,7 +4529,7 @@
         <v>0.9203</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9942</v>
+        <v>0.9991</v>
       </c>
       <c r="H72" t="n">
         <v>0.875</v>
@@ -4538,25 +4538,25 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9224</v>
+        <v>0.9226</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1295</v>
+        <v>0.0263</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1883.9</v>
+        <v>282.7</v>
       </c>
       <c r="Q72" t="n">
         <v>13885</v>
@@ -4586,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.988</v>
+        <v>0.9991</v>
       </c>
       <c r="H73" t="n">
         <v>0.8125</v>
@@ -4595,25 +4595,25 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9549</v>
+        <v>0.9565</v>
       </c>
       <c r="N73" t="n">
-        <v>0.132</v>
+        <v>0.0262</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2125.2</v>
+        <v>277</v>
       </c>
       <c r="Q73" t="n">
         <v>12828</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9932</v>
+        <v>0.999</v>
       </c>
       <c r="H74" t="n">
         <v>0.0625</v>
@@ -4652,25 +4652,25 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K74" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7837</v>
+        <v>0.7829</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1526</v>
+        <v>0.0287</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1873.3</v>
+        <v>264.9</v>
       </c>
       <c r="Q74" t="n">
         <v>10805</v>
@@ -4700,7 +4700,7 @@
         <v>0.9193</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9952</v>
+        <v>0.9993</v>
       </c>
       <c r="H75" t="n">
         <v>0.3125</v>
@@ -4709,25 +4709,25 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1354</v>
+        <v>0.0256</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1688.3</v>
+        <v>255.5</v>
       </c>
       <c r="Q75" t="n">
         <v>11954</v>
@@ -4757,7 +4757,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="H76" t="n">
         <v>0.5625</v>
@@ -4766,25 +4766,25 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M76" t="n">
-        <v>0.844</v>
+        <v>0.8439</v>
       </c>
       <c r="N76" t="n">
-        <v>0.1878</v>
+        <v>0.0347</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1711.7</v>
+        <v>271.8</v>
       </c>
       <c r="Q76" t="n">
         <v>8299</v>
@@ -4814,7 +4814,7 @@
         <v>0.9466</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9937</v>
+        <v>0.9991</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -4823,25 +4823,25 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7373</v>
+        <v>0.7361</v>
       </c>
       <c r="N77" t="n">
-        <v>0.1481</v>
+        <v>0.0267</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1928.2</v>
+        <v>262</v>
       </c>
       <c r="Q77" t="n">
         <v>10391</v>
@@ -4871,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.992</v>
+        <v>0.9988</v>
       </c>
       <c r="H78" t="n">
         <v>0.625</v>
@@ -4880,25 +4880,25 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M78" t="n">
-        <v>0.9126</v>
+        <v>0.913</v>
       </c>
       <c r="N78" t="n">
-        <v>0.2502</v>
+        <v>0.0374</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1478.8</v>
+        <v>228.4</v>
       </c>
       <c r="Q78" t="n">
         <v>4966</v>
@@ -4928,7 +4928,7 @@
         <v>0.9353</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9964</v>
+        <v>0.9991</v>
       </c>
       <c r="H79" t="n">
         <v>0.6875</v>
@@ -4937,25 +4937,25 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8887</v>
+        <v>0.8883</v>
       </c>
       <c r="N79" t="n">
-        <v>0.1439</v>
+        <v>0.0284</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>914.8</v>
+        <v>235.6</v>
       </c>
       <c r="Q79" t="n">
         <v>6437</v>
@@ -4985,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9928</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H80" t="n">
         <v>0.1562</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8051</v>
+        <v>0.8045</v>
       </c>
       <c r="N80" t="n">
-        <v>0.1862</v>
+        <v>0.0415</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1089.9</v>
+        <v>235.6</v>
       </c>
       <c r="Q80" t="n">
         <v>4414</v>
@@ -5042,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9958</v>
+        <v>0.9989</v>
       </c>
       <c r="H81" t="n">
         <v>0.09370000000000001</v>
@@ -5051,25 +5051,25 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.6016</v>
+        <v>0.6065</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1689</v>
+        <v>0.1621</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2295</v>
+        <v>0.2314</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7913</v>
+        <v>0.7901</v>
       </c>
       <c r="N81" t="n">
-        <v>0.1267</v>
+        <v>0.0295</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>858.5</v>
+        <v>220.9</v>
       </c>
       <c r="Q81" t="n">
         <v>5931</v>
@@ -5099,7 +5099,7 @@
         <v>0.9203</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9235</v>
+        <v>0.999</v>
       </c>
       <c r="H82" t="n">
         <v>0.875</v>
@@ -5108,25 +5108,25 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9226</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1554</v>
+        <v>0.0316</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2260.7</v>
+        <v>339.2</v>
       </c>
       <c r="Q82" t="n">
         <v>13885</v>
@@ -5156,37 +5156,37 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7856</v>
+        <v>0.9989</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3438</v>
+        <v>0.8125</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8565</v>
+        <v>0.9564</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1572</v>
+        <v>0.0315</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2550.2</v>
+        <v>332.4</v>
       </c>
       <c r="Q83" t="n">
-        <v>12920</v>
+        <v>12828</v>
       </c>
     </row>
     <row r="84">
@@ -5213,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9296</v>
+        <v>0.9988</v>
       </c>
       <c r="H84" t="n">
         <v>0.0625</v>
@@ -5222,25 +5222,25 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9195</v>
+        <v>0.7829</v>
       </c>
       <c r="N84" t="n">
-        <v>0.1831</v>
+        <v>0.0344</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2247.9</v>
+        <v>317.8</v>
       </c>
       <c r="Q84" t="n">
         <v>10805</v>
@@ -5270,7 +5270,7 @@
         <v>0.9193</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9942</v>
+        <v>0.9991</v>
       </c>
       <c r="H85" t="n">
         <v>0.3125</v>
@@ -5279,25 +5279,25 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9308</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1625</v>
+        <v>0.0307</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2026</v>
+        <v>306.6</v>
       </c>
       <c r="Q85" t="n">
         <v>11954</v>
@@ -5327,7 +5327,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9909</v>
+        <v>0.9986</v>
       </c>
       <c r="H86" t="n">
         <v>0.5625</v>
@@ -5336,25 +5336,25 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M86" t="n">
-        <v>0.9366</v>
+        <v>0.8438</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2253</v>
+        <v>0.0416</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2054.1</v>
+        <v>326.1</v>
       </c>
       <c r="Q86" t="n">
         <v>8299</v>
@@ -5384,7 +5384,7 @@
         <v>0.9466</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8982</v>
+        <v>0.999</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -5393,25 +5393,25 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M87" t="n">
-        <v>0.8773</v>
+        <v>0.736</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1778</v>
+        <v>0.032</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2313.8</v>
+        <v>314.4</v>
       </c>
       <c r="Q87" t="n">
         <v>10391</v>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9905</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H88" t="n">
         <v>0.625</v>
@@ -5450,25 +5450,25 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9776</v>
+        <v>0.913</v>
       </c>
       <c r="N88" t="n">
-        <v>0.3003</v>
+        <v>0.0449</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1774.6</v>
+        <v>274.1</v>
       </c>
       <c r="Q88" t="n">
         <v>4966</v>
@@ -5498,7 +5498,7 @@
         <v>0.9353</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9957</v>
+        <v>0.9989</v>
       </c>
       <c r="H89" t="n">
         <v>0.6875</v>
@@ -5507,25 +5507,25 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M89" t="n">
-        <v>0.9557</v>
+        <v>0.8883</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1727</v>
+        <v>0.0341</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1097.8</v>
+        <v>282.7</v>
       </c>
       <c r="Q89" t="n">
         <v>6437</v>
@@ -5555,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="H90" t="n">
         <v>0.1562</v>
@@ -5564,25 +5564,25 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M90" t="n">
-        <v>0.9565</v>
+        <v>0.8044</v>
       </c>
       <c r="N90" t="n">
-        <v>0.2235</v>
+        <v>0.0498</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1307.9</v>
+        <v>282.7</v>
       </c>
       <c r="Q90" t="n">
         <v>4414</v>
@@ -5612,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.995</v>
+        <v>0.9987</v>
       </c>
       <c r="H91" t="n">
         <v>0.09370000000000001</v>
@@ -5621,25 +5621,25 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.4257</v>
+        <v>0.6065</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5281</v>
+        <v>0.1621</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0462</v>
+        <v>0.2314</v>
       </c>
       <c r="M91" t="n">
-        <v>0.9555</v>
+        <v>0.7901</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1521</v>
+        <v>0.0354</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1030.2</v>
+        <v>265.1</v>
       </c>
       <c r="Q91" t="n">
         <v>5931</v>

--- a/results/q4_output/健康度评价.xlsx
+++ b/results/q4_output/健康度评价.xlsx
@@ -539,7 +539,7 @@
         <v>0.9203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9993</v>
+        <v>0.9956</v>
       </c>
       <c r="H2" t="n">
         <v>0.875</v>
@@ -548,25 +548,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0219</v>
+        <v>0.1503</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>235.6</v>
+        <v>1424.9</v>
       </c>
       <c r="Q2" t="n">
         <v>13885</v>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9992</v>
+        <v>0.9951</v>
       </c>
       <c r="H3" t="n">
         <v>0.8125</v>
@@ -605,25 +605,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0219</v>
+        <v>0.1509</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>230.8</v>
+        <v>1457.3</v>
       </c>
       <c r="Q3" t="n">
         <v>12828</v>
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9992</v>
+        <v>0.9941</v>
       </c>
       <c r="H4" t="n">
         <v>0.0625</v>
@@ -662,25 +662,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0239</v>
+        <v>0.1744</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>220.7</v>
+        <v>1637.4</v>
       </c>
       <c r="Q4" t="n">
         <v>10805</v>
@@ -710,7 +710,7 @@
         <v>0.9193</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9994</v>
+        <v>0.9954</v>
       </c>
       <c r="H5" t="n">
         <v>0.3125</v>
@@ -719,25 +719,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7919</v>
+        <v>0.7638</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0213</v>
+        <v>0.1386</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>212.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q5" t="n">
         <v>11954</v>
@@ -767,7 +767,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.999</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>0.5625</v>
@@ -776,25 +776,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0289</v>
+        <v>0.1628</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>226.5</v>
+        <v>1231.2</v>
       </c>
       <c r="Q6" t="n">
         <v>8299</v>
@@ -824,7 +824,7 @@
         <v>0.9466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9993</v>
+        <v>0.9978</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -833,25 +833,25 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7361</v>
+        <v>0.7007</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0222</v>
+        <v>0.1022</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>218.3</v>
+        <v>672.1</v>
       </c>
       <c r="Q7" t="n">
         <v>10391</v>
@@ -881,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.999</v>
+        <v>0.9976</v>
       </c>
       <c r="H8" t="n">
         <v>0.625</v>
@@ -890,25 +890,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9131</v>
+        <v>0.9014</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0312</v>
+        <v>0.1013</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>190.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q8" t="n">
         <v>4966</v>
@@ -938,7 +938,7 @@
         <v>0.9353</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9992</v>
+        <v>0.9973</v>
       </c>
       <c r="H9" t="n">
         <v>0.6875</v>
@@ -947,25 +947,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0237</v>
+        <v>0.0759</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>196.3</v>
+        <v>678.5</v>
       </c>
       <c r="Q9" t="n">
         <v>6437</v>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9987</v>
+        <v>0.9989</v>
       </c>
       <c r="H10" t="n">
         <v>0.1562</v>
@@ -1004,25 +1004,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8045</v>
+        <v>0.7785</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0346</v>
+        <v>0.0324</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>196.3</v>
+        <v>165.7</v>
       </c>
       <c r="Q10" t="n">
         <v>4414</v>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="H11" t="n">
         <v>0.09370000000000001</v>
@@ -1061,25 +1061,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0246</v>
+        <v>0.005</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>184.1</v>
+        <v>55.1</v>
       </c>
       <c r="Q11" t="n">
         <v>5931</v>
@@ -1109,7 +1109,7 @@
         <v>0.9203</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9992</v>
+        <v>0.9952</v>
       </c>
       <c r="H12" t="n">
         <v>0.875</v>
@@ -1118,25 +1118,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0241</v>
+        <v>0.1653</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>259.1</v>
+        <v>1567.4</v>
       </c>
       <c r="Q12" t="n">
         <v>13885</v>
@@ -1166,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9991</v>
+        <v>0.9946</v>
       </c>
       <c r="H13" t="n">
         <v>0.8125</v>
@@ -1175,25 +1175,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N13" t="n">
-        <v>0.024</v>
+        <v>0.166</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>253.9</v>
+        <v>1603</v>
       </c>
       <c r="Q13" t="n">
         <v>12828</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9991</v>
+        <v>0.9935</v>
       </c>
       <c r="H14" t="n">
         <v>0.0625</v>
@@ -1232,25 +1232,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0263</v>
+        <v>0.1918</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>242.8</v>
+        <v>1801.2</v>
       </c>
       <c r="Q14" t="n">
         <v>10805</v>
@@ -1280,7 +1280,7 @@
         <v>0.9193</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9993</v>
+        <v>0.9949</v>
       </c>
       <c r="H15" t="n">
         <v>0.3125</v>
@@ -1289,25 +1289,25 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0234</v>
+        <v>0.1524</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>234.2</v>
+        <v>1799.2</v>
       </c>
       <c r="Q15" t="n">
         <v>11954</v>
@@ -1337,7 +1337,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9989</v>
+        <v>0.994</v>
       </c>
       <c r="H16" t="n">
         <v>0.5625</v>
@@ -1346,25 +1346,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0318</v>
+        <v>0.179</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>249.1</v>
+        <v>1354.3</v>
       </c>
       <c r="Q16" t="n">
         <v>8299</v>
@@ -1394,7 +1394,7 @@
         <v>0.9466</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9992</v>
+        <v>0.9976</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1403,25 +1403,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7361</v>
+        <v>0.7006</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0244</v>
+        <v>0.1125</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>240.2</v>
+        <v>739.3</v>
       </c>
       <c r="Q17" t="n">
         <v>10391</v>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9989</v>
+        <v>0.9974</v>
       </c>
       <c r="H18" t="n">
         <v>0.625</v>
@@ -1460,25 +1460,25 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M18" t="n">
-        <v>0.913</v>
+        <v>0.9014</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0343</v>
+        <v>0.1114</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>209.4</v>
+        <v>488.3</v>
       </c>
       <c r="Q18" t="n">
         <v>4966</v>
@@ -1508,7 +1508,7 @@
         <v>0.9353</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9992</v>
+        <v>0.9971</v>
       </c>
       <c r="H19" t="n">
         <v>0.6875</v>
@@ -1517,25 +1517,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0261</v>
+        <v>0.0835</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>215.9</v>
+        <v>746.4</v>
       </c>
       <c r="Q19" t="n">
         <v>6437</v>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9986</v>
+        <v>0.9988</v>
       </c>
       <c r="H20" t="n">
         <v>0.1562</v>
@@ -1574,25 +1574,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8045</v>
+        <v>0.7785</v>
       </c>
       <c r="N20" t="n">
-        <v>0.038</v>
+        <v>0.0357</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>215.9</v>
+        <v>182.3</v>
       </c>
       <c r="Q20" t="n">
         <v>4414</v>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.999</v>
+        <v>0.9997</v>
       </c>
       <c r="H21" t="n">
         <v>0.09370000000000001</v>
@@ -1631,25 +1631,25 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N21" t="n">
-        <v>0.027</v>
+        <v>0.0055</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>202.5</v>
+        <v>60.6</v>
       </c>
       <c r="Q21" t="n">
         <v>5931</v>
@@ -1679,7 +1679,7 @@
         <v>0.9203</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9991</v>
+        <v>0.9947</v>
       </c>
       <c r="H22" t="n">
         <v>0.875</v>
@@ -1688,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0265</v>
+        <v>0.1818</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>285</v>
+        <v>1724.2</v>
       </c>
       <c r="Q22" t="n">
         <v>13885</v>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9991</v>
+        <v>0.9941</v>
       </c>
       <c r="H23" t="n">
         <v>0.8125</v>
@@ -1745,25 +1745,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0264</v>
+        <v>0.1826</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>279.3</v>
+        <v>1763.3</v>
       </c>
       <c r="Q23" t="n">
         <v>12828</v>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.999</v>
+        <v>0.9928</v>
       </c>
       <c r="H24" t="n">
         <v>0.0625</v>
@@ -1802,25 +1802,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7829</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0289</v>
+        <v>0.211</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>267.1</v>
+        <v>1981.3</v>
       </c>
       <c r="Q24" t="n">
         <v>10805</v>
@@ -1850,7 +1850,7 @@
         <v>0.9193</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9993</v>
+        <v>0.9944</v>
       </c>
       <c r="H25" t="n">
         <v>0.3125</v>
@@ -1859,25 +1859,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0258</v>
+        <v>0.1677</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>257.6</v>
+        <v>1979.1</v>
       </c>
       <c r="Q25" t="n">
         <v>11954</v>
@@ -1907,7 +1907,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9988</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0.5625</v>
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N26" t="n">
-        <v>0.035</v>
+        <v>0.1969</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>274</v>
+        <v>1489.7</v>
       </c>
       <c r="Q26" t="n">
         <v>8299</v>
@@ -1964,7 +1964,7 @@
         <v>0.9466</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9991</v>
+        <v>0.9974</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1973,25 +1973,25 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7361</v>
+        <v>0.7006</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0269</v>
+        <v>0.1237</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>264.2</v>
+        <v>813.2</v>
       </c>
       <c r="Q27" t="n">
         <v>10391</v>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9988</v>
+        <v>0.9971</v>
       </c>
       <c r="H28" t="n">
         <v>0.625</v>
@@ -2030,25 +2030,25 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M28" t="n">
-        <v>0.913</v>
+        <v>0.9014</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0377</v>
+        <v>0.1225</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>230.4</v>
+        <v>537.1</v>
       </c>
       <c r="Q28" t="n">
         <v>4966</v>
@@ -2078,7 +2078,7 @@
         <v>0.9353</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9991</v>
+        <v>0.9968</v>
       </c>
       <c r="H29" t="n">
         <v>0.6875</v>
@@ -2087,25 +2087,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0287</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>237.5</v>
+        <v>821</v>
       </c>
       <c r="Q29" t="n">
         <v>6437</v>
@@ -2135,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9984</v>
+        <v>0.9987</v>
       </c>
       <c r="H30" t="n">
         <v>0.1562</v>
@@ -2144,25 +2144,25 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8045</v>
+        <v>0.7784</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0418</v>
+        <v>0.0393</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>237.5</v>
+        <v>200.6</v>
       </c>
       <c r="Q30" t="n">
         <v>4414</v>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9989</v>
+        <v>0.9997</v>
       </c>
       <c r="H31" t="n">
         <v>0.09370000000000001</v>
@@ -2201,25 +2201,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0297</v>
+        <v>0.006</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>222.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>5931</v>
@@ -2249,7 +2249,7 @@
         <v>0.9203</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9993</v>
+        <v>0.9956</v>
       </c>
       <c r="H32" t="n">
         <v>0.875</v>
@@ -2258,25 +2258,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0219</v>
+        <v>0.1503</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>235.6</v>
+        <v>1424.9</v>
       </c>
       <c r="Q32" t="n">
         <v>13885</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9992</v>
+        <v>0.9951</v>
       </c>
       <c r="H33" t="n">
         <v>0.8125</v>
@@ -2315,25 +2315,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0219</v>
+        <v>0.1509</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>230.8</v>
+        <v>1457.3</v>
       </c>
       <c r="Q33" t="n">
         <v>12828</v>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9992</v>
+        <v>0.9941</v>
       </c>
       <c r="H34" t="n">
         <v>0.0625</v>
@@ -2372,25 +2372,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0239</v>
+        <v>0.1744</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>220.7</v>
+        <v>1637.4</v>
       </c>
       <c r="Q34" t="n">
         <v>10805</v>
@@ -2420,7 +2420,7 @@
         <v>0.9193</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9994</v>
+        <v>0.9954</v>
       </c>
       <c r="H35" t="n">
         <v>0.3125</v>
@@ -2429,25 +2429,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7919</v>
+        <v>0.7638</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0213</v>
+        <v>0.1386</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>212.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q35" t="n">
         <v>11954</v>
@@ -2477,7 +2477,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.999</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>0.5625</v>
@@ -2486,25 +2486,25 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0289</v>
+        <v>0.1628</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>226.5</v>
+        <v>1231.2</v>
       </c>
       <c r="Q36" t="n">
         <v>8299</v>
@@ -2534,7 +2534,7 @@
         <v>0.9466</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9993</v>
+        <v>0.9978</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2543,25 +2543,25 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7361</v>
+        <v>0.7007</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0222</v>
+        <v>0.1022</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>218.3</v>
+        <v>672.1</v>
       </c>
       <c r="Q37" t="n">
         <v>10391</v>
@@ -2591,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.999</v>
+        <v>0.9976</v>
       </c>
       <c r="H38" t="n">
         <v>0.625</v>
@@ -2600,25 +2600,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9131</v>
+        <v>0.9014</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0312</v>
+        <v>0.1013</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>190.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q38" t="n">
         <v>4966</v>
@@ -2648,7 +2648,7 @@
         <v>0.9353</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9992</v>
+        <v>0.9973</v>
       </c>
       <c r="H39" t="n">
         <v>0.6875</v>
@@ -2657,25 +2657,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0237</v>
+        <v>0.0759</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>196.3</v>
+        <v>678.5</v>
       </c>
       <c r="Q39" t="n">
         <v>6437</v>
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9987</v>
+        <v>0.9989</v>
       </c>
       <c r="H40" t="n">
         <v>0.1562</v>
@@ -2714,25 +2714,25 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8045</v>
+        <v>0.7785</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0346</v>
+        <v>0.0324</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>196.3</v>
+        <v>165.7</v>
       </c>
       <c r="Q40" t="n">
         <v>4414</v>
@@ -2762,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="H41" t="n">
         <v>0.09370000000000001</v>
@@ -2771,25 +2771,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0246</v>
+        <v>0.005</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>184.1</v>
+        <v>55.1</v>
       </c>
       <c r="Q41" t="n">
         <v>5931</v>
@@ -2819,7 +2819,7 @@
         <v>0.9203</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9992</v>
+        <v>0.995</v>
       </c>
       <c r="H42" t="n">
         <v>0.875</v>
@@ -2828,25 +2828,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0252</v>
+        <v>0.1728</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>270.9</v>
+        <v>1638.7</v>
       </c>
       <c r="Q42" t="n">
         <v>13885</v>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9991</v>
+        <v>0.9944</v>
       </c>
       <c r="H43" t="n">
         <v>0.8125</v>
@@ -2885,25 +2885,25 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0251</v>
+        <v>0.1736</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>265.5</v>
+        <v>1675.8</v>
       </c>
       <c r="Q43" t="n">
         <v>12828</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9991</v>
+        <v>0.9932</v>
       </c>
       <c r="H44" t="n">
         <v>0.0625</v>
@@ -2942,25 +2942,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0275</v>
+        <v>0.2005</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>253.8</v>
+        <v>1883</v>
       </c>
       <c r="Q44" t="n">
         <v>10805</v>
@@ -2990,7 +2990,7 @@
         <v>0.9193</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9993</v>
+        <v>0.9947</v>
       </c>
       <c r="H45" t="n">
         <v>0.3125</v>
@@ -2999,25 +2999,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0245</v>
+        <v>0.1594</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>244.9</v>
+        <v>1881</v>
       </c>
       <c r="Q45" t="n">
         <v>11954</v>
@@ -3047,7 +3047,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9988</v>
+        <v>0.9937</v>
       </c>
       <c r="H46" t="n">
         <v>0.5625</v>
@@ -3056,25 +3056,25 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0332</v>
+        <v>0.1872</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>260.5</v>
+        <v>1415.8</v>
       </c>
       <c r="Q46" t="n">
         <v>8299</v>
@@ -3104,7 +3104,7 @@
         <v>0.9466</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9992</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3113,25 +3113,25 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7361</v>
+        <v>0.7006</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0255</v>
+        <v>0.1176</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>251.1</v>
+        <v>772.9</v>
       </c>
       <c r="Q47" t="n">
         <v>10391</v>
@@ -3161,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9988</v>
+        <v>0.9973</v>
       </c>
       <c r="H48" t="n">
         <v>0.625</v>
@@ -3170,25 +3170,25 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M48" t="n">
-        <v>0.913</v>
+        <v>0.9014</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0358</v>
+        <v>0.1164</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>218.9</v>
+        <v>510.5</v>
       </c>
       <c r="Q48" t="n">
         <v>4966</v>
@@ -3218,7 +3218,7 @@
         <v>0.9353</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9991</v>
+        <v>0.9969</v>
       </c>
       <c r="H49" t="n">
         <v>0.6875</v>
@@ -3227,25 +3227,25 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0273</v>
+        <v>0.0873</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>225.7</v>
+        <v>780.3</v>
       </c>
       <c r="Q49" t="n">
         <v>6437</v>
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9987</v>
       </c>
       <c r="H50" t="n">
         <v>0.1562</v>
@@ -3284,25 +3284,25 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8045</v>
+        <v>0.7785</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0398</v>
+        <v>0.0373</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>225.7</v>
+        <v>190.6</v>
       </c>
       <c r="Q50" t="n">
         <v>4414</v>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.999</v>
+        <v>0.9997</v>
       </c>
       <c r="H51" t="n">
         <v>0.09370000000000001</v>
@@ -3341,25 +3341,25 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0283</v>
+        <v>0.0057</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>211.7</v>
+        <v>63.3</v>
       </c>
       <c r="Q51" t="n">
         <v>5931</v>
@@ -3389,7 +3389,7 @@
         <v>0.9203</v>
       </c>
       <c r="G52" t="n">
-        <v>0.999</v>
+        <v>0.9942</v>
       </c>
       <c r="H52" t="n">
         <v>0.875</v>
@@ -3398,25 +3398,25 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9226</v>
+        <v>0.9486</v>
       </c>
       <c r="N52" t="n">
-        <v>0.029</v>
+        <v>0.1987</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>311.5</v>
+        <v>1884.5</v>
       </c>
       <c r="Q52" t="n">
         <v>13885</v>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.999</v>
+        <v>0.9935</v>
       </c>
       <c r="H53" t="n">
         <v>0.8125</v>
@@ -3455,25 +3455,25 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9564</v>
+        <v>0.9696</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0289</v>
+        <v>0.1996</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>305.3</v>
+        <v>1927.2</v>
       </c>
       <c r="Q53" t="n">
         <v>12828</v>
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9989</v>
+        <v>0.9688</v>
       </c>
       <c r="H54" t="n">
         <v>0.0625</v>
@@ -3512,25 +3512,25 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7829</v>
+        <v>0.8487</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0316</v>
+        <v>0.2306</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>291.9</v>
+        <v>2165.5</v>
       </c>
       <c r="Q54" t="n">
         <v>10805</v>
@@ -3560,7 +3560,7 @@
         <v>0.9193</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9992</v>
+        <v>0.9699</v>
       </c>
       <c r="H55" t="n">
         <v>0.3125</v>
@@ -3569,25 +3569,25 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8548</v>
       </c>
       <c r="N55" t="n">
-        <v>0.0282</v>
+        <v>0.1833</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>281.6</v>
+        <v>2163.1</v>
       </c>
       <c r="Q55" t="n">
         <v>11954</v>
@@ -3617,7 +3617,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9987</v>
+        <v>0.9928</v>
       </c>
       <c r="H56" t="n">
         <v>0.5625</v>
@@ -3626,25 +3626,25 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8438</v>
+        <v>0.8984</v>
       </c>
       <c r="N56" t="n">
-        <v>0.0382</v>
+        <v>0.2152</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>299.5</v>
+        <v>1628.2</v>
       </c>
       <c r="Q56" t="n">
         <v>8299</v>
@@ -3674,7 +3674,7 @@
         <v>0.9466</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9991</v>
+        <v>0.9971</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3683,25 +3683,25 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M57" t="n">
-        <v>0.736</v>
+        <v>0.8325</v>
       </c>
       <c r="N57" t="n">
-        <v>0.0294</v>
+        <v>0.1352</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>288.8</v>
+        <v>888.8</v>
       </c>
       <c r="Q57" t="n">
         <v>10391</v>
@@ -3731,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9986</v>
+        <v>0.9968</v>
       </c>
       <c r="H58" t="n">
         <v>0.625</v>
@@ -3740,25 +3740,25 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M58" t="n">
-        <v>0.913</v>
+        <v>0.9439</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0412</v>
+        <v>0.1339</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>251.8</v>
+        <v>587.1</v>
       </c>
       <c r="Q58" t="n">
         <v>4966</v>
@@ -3788,7 +3788,7 @@
         <v>0.9353</v>
       </c>
       <c r="G59" t="n">
-        <v>0.999</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0.6875</v>
@@ -3797,25 +3797,25 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M59" t="n">
-        <v>0.8883</v>
+        <v>0.9281</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0314</v>
+        <v>0.1003</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>259.6</v>
+        <v>897.3</v>
       </c>
       <c r="Q59" t="n">
         <v>6437</v>
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9983</v>
+        <v>0.9986</v>
       </c>
       <c r="H60" t="n">
         <v>0.1562</v>
@@ -3854,25 +3854,25 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8045</v>
+        <v>0.8764</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0457</v>
+        <v>0.0429</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>259.6</v>
+        <v>219.2</v>
       </c>
       <c r="Q60" t="n">
         <v>4414</v>
@@ -3902,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9988</v>
+        <v>0.9996</v>
       </c>
       <c r="H61" t="n">
         <v>0.09370000000000001</v>
@@ -3911,25 +3911,25 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6065</v>
+        <v>0.3819</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1621</v>
+        <v>0.4724</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2314</v>
+        <v>0.1457</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7901</v>
+        <v>0.8678</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0325</v>
+        <v>0.0066</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>243.5</v>
+        <v>72.8</v>
       </c>
       <c r="Q61" t="n">
         <v>5931</v>
@@ -3959,7 +3959,7 @@
         <v>0.9203</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9993</v>
+        <v>0.9956</v>
       </c>
       <c r="H62" t="n">
         <v>0.875</v>
@@ -3968,25 +3968,25 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N62" t="n">
-        <v>0.0219</v>
+        <v>0.1503</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>235.6</v>
+        <v>1424.9</v>
       </c>
       <c r="Q62" t="n">
         <v>13885</v>
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9992</v>
+        <v>0.9951</v>
       </c>
       <c r="H63" t="n">
         <v>0.8125</v>
@@ -4025,25 +4025,25 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0219</v>
+        <v>0.1509</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>230.8</v>
+        <v>1457.3</v>
       </c>
       <c r="Q63" t="n">
         <v>12828</v>
@@ -4073,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9992</v>
+        <v>0.9941</v>
       </c>
       <c r="H64" t="n">
         <v>0.0625</v>
@@ -4082,25 +4082,25 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0239</v>
+        <v>0.1744</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>220.7</v>
+        <v>1637.4</v>
       </c>
       <c r="Q64" t="n">
         <v>10805</v>
@@ -4130,7 +4130,7 @@
         <v>0.9193</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9994</v>
+        <v>0.9954</v>
       </c>
       <c r="H65" t="n">
         <v>0.3125</v>
@@ -4139,25 +4139,25 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7919</v>
+        <v>0.7638</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0213</v>
+        <v>0.1386</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>212.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q65" t="n">
         <v>11954</v>
@@ -4187,7 +4187,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.999</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H66" t="n">
         <v>0.5625</v>
@@ -4196,25 +4196,25 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0289</v>
+        <v>0.1628</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>226.5</v>
+        <v>1231.2</v>
       </c>
       <c r="Q66" t="n">
         <v>8299</v>
@@ -4244,7 +4244,7 @@
         <v>0.9466</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9993</v>
+        <v>0.9978</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -4253,25 +4253,25 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7361</v>
+        <v>0.7007</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0222</v>
+        <v>0.1022</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>218.3</v>
+        <v>672.1</v>
       </c>
       <c r="Q67" t="n">
         <v>10391</v>
@@ -4301,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.999</v>
+        <v>0.9976</v>
       </c>
       <c r="H68" t="n">
         <v>0.625</v>
@@ -4310,25 +4310,25 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9131</v>
+        <v>0.9014</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0312</v>
+        <v>0.1013</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>190.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q68" t="n">
         <v>4966</v>
@@ -4358,7 +4358,7 @@
         <v>0.9353</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9992</v>
+        <v>0.9973</v>
       </c>
       <c r="H69" t="n">
         <v>0.6875</v>
@@ -4367,25 +4367,25 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0237</v>
+        <v>0.0759</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>196.3</v>
+        <v>678.5</v>
       </c>
       <c r="Q69" t="n">
         <v>6437</v>
@@ -4415,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9987</v>
+        <v>0.9989</v>
       </c>
       <c r="H70" t="n">
         <v>0.1562</v>
@@ -4424,25 +4424,25 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M70" t="n">
-        <v>0.8045</v>
+        <v>0.7785</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0346</v>
+        <v>0.0324</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>196.3</v>
+        <v>165.7</v>
       </c>
       <c r="Q70" t="n">
         <v>4414</v>
@@ -4472,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="H71" t="n">
         <v>0.09370000000000001</v>
@@ -4481,25 +4481,25 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0246</v>
+        <v>0.005</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>184.1</v>
+        <v>55.1</v>
       </c>
       <c r="Q71" t="n">
         <v>5931</v>
@@ -4529,7 +4529,7 @@
         <v>0.9203</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9991</v>
+        <v>0.9947</v>
       </c>
       <c r="H72" t="n">
         <v>0.875</v>
@@ -4538,25 +4538,25 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9226</v>
+        <v>0.9121</v>
       </c>
       <c r="N72" t="n">
-        <v>0.0263</v>
+        <v>0.1803</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>282.7</v>
+        <v>1709.9</v>
       </c>
       <c r="Q72" t="n">
         <v>13885</v>
@@ -4586,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9991</v>
+        <v>0.9941</v>
       </c>
       <c r="H73" t="n">
         <v>0.8125</v>
@@ -4595,25 +4595,25 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="N73" t="n">
-        <v>0.0262</v>
+        <v>0.1811</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>277</v>
+        <v>1748.7</v>
       </c>
       <c r="Q73" t="n">
         <v>12828</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.999</v>
+        <v>0.9929</v>
       </c>
       <c r="H74" t="n">
         <v>0.0625</v>
@@ -4652,25 +4652,25 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0287</v>
+        <v>0.2092</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>264.9</v>
+        <v>1964.9</v>
       </c>
       <c r="Q74" t="n">
         <v>10805</v>
@@ -4700,7 +4700,7 @@
         <v>0.9193</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9993</v>
+        <v>0.9944</v>
       </c>
       <c r="H75" t="n">
         <v>0.3125</v>
@@ -4709,25 +4709,25 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="N75" t="n">
-        <v>0.0256</v>
+        <v>0.1663</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>255.5</v>
+        <v>1962.7</v>
       </c>
       <c r="Q75" t="n">
         <v>11954</v>
@@ -4757,7 +4757,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9988</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>0.5625</v>
@@ -4766,25 +4766,25 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8439</v>
+        <v>0.8228</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0347</v>
+        <v>0.1953</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>271.8</v>
+        <v>1477.4</v>
       </c>
       <c r="Q76" t="n">
         <v>8299</v>
@@ -4814,7 +4814,7 @@
         <v>0.9466</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9991</v>
+        <v>0.9974</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -4823,25 +4823,25 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7361</v>
+        <v>0.7006</v>
       </c>
       <c r="N77" t="n">
-        <v>0.0267</v>
+        <v>0.1227</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>262</v>
+        <v>806.5</v>
       </c>
       <c r="Q77" t="n">
         <v>10391</v>
@@ -4871,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9988</v>
+        <v>0.9971</v>
       </c>
       <c r="H78" t="n">
         <v>0.625</v>
@@ -4880,25 +4880,25 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M78" t="n">
-        <v>0.913</v>
+        <v>0.9014</v>
       </c>
       <c r="N78" t="n">
-        <v>0.0374</v>
+        <v>0.1215</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>228.4</v>
+        <v>532.7</v>
       </c>
       <c r="Q78" t="n">
         <v>4966</v>
@@ -4928,7 +4928,7 @@
         <v>0.9353</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9991</v>
+        <v>0.9968</v>
       </c>
       <c r="H79" t="n">
         <v>0.6875</v>
@@ -4937,25 +4937,25 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="N79" t="n">
-        <v>0.0284</v>
+        <v>0.091</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>235.6</v>
+        <v>814.2</v>
       </c>
       <c r="Q79" t="n">
         <v>6437</v>
@@ -4985,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9987</v>
       </c>
       <c r="H80" t="n">
         <v>0.1562</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8045</v>
+        <v>0.7784</v>
       </c>
       <c r="N80" t="n">
-        <v>0.0415</v>
+        <v>0.0389</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>235.6</v>
+        <v>198.9</v>
       </c>
       <c r="Q80" t="n">
         <v>4414</v>
@@ -5042,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9989</v>
+        <v>0.9997</v>
       </c>
       <c r="H81" t="n">
         <v>0.09370000000000001</v>
@@ -5051,25 +5051,25 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.6065</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1621</v>
+        <v>0.0495</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2314</v>
+        <v>0.2625</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7901</v>
+        <v>0.7621</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0295</v>
+        <v>0.006</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>220.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q81" t="n">
         <v>5931</v>
@@ -5099,7 +5099,7 @@
         <v>0.9203</v>
       </c>
       <c r="G82" t="n">
-        <v>0.999</v>
+        <v>0.9937</v>
       </c>
       <c r="H82" t="n">
         <v>0.875</v>
@@ -5108,25 +5108,25 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L82" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9226</v>
+        <v>0.9569</v>
       </c>
       <c r="N82" t="n">
-        <v>0.0316</v>
+        <v>0.2164</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>339.2</v>
+        <v>2051.9</v>
       </c>
       <c r="Q82" t="n">
         <v>13885</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9989</v>
+        <v>0.993</v>
       </c>
       <c r="H83" t="n">
         <v>0.8125</v>
@@ -5165,25 +5165,25 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L83" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M83" t="n">
-        <v>0.9564</v>
+        <v>0.9738</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0315</v>
+        <v>0.2173</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>332.4</v>
+        <v>2098.5</v>
       </c>
       <c r="Q83" t="n">
         <v>12828</v>
@@ -5213,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9988</v>
+        <v>0.8772</v>
       </c>
       <c r="H84" t="n">
         <v>0.0625</v>
@@ -5222,25 +5222,25 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M84" t="n">
-        <v>0.7829</v>
+        <v>0.8189</v>
       </c>
       <c r="N84" t="n">
-        <v>0.0344</v>
+        <v>0.2511</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>317.8</v>
+        <v>2357.9</v>
       </c>
       <c r="Q84" t="n">
         <v>10805</v>
@@ -5270,7 +5270,7 @@
         <v>0.9193</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9991</v>
+        <v>0.8784</v>
       </c>
       <c r="H85" t="n">
         <v>0.3125</v>
@@ -5279,25 +5279,25 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>0.0307</v>
+        <v>0.1996</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>306.6</v>
+        <v>2355.3</v>
       </c>
       <c r="Q85" t="n">
         <v>11954</v>
@@ -5327,7 +5327,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9986</v>
+        <v>0.9921</v>
       </c>
       <c r="H86" t="n">
         <v>0.5625</v>
@@ -5336,25 +5336,25 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8438</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>0.0416</v>
+        <v>0.2344</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>326.1</v>
+        <v>1772.9</v>
       </c>
       <c r="Q86" t="n">
         <v>8299</v>
@@ -5384,7 +5384,7 @@
         <v>0.9466</v>
       </c>
       <c r="G87" t="n">
-        <v>0.999</v>
+        <v>0.9969</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -5393,25 +5393,25 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M87" t="n">
-        <v>0.736</v>
+        <v>0.8633</v>
       </c>
       <c r="N87" t="n">
-        <v>0.032</v>
+        <v>0.1472</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>314.4</v>
+        <v>967.8</v>
       </c>
       <c r="Q87" t="n">
         <v>10391</v>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9966</v>
       </c>
       <c r="H88" t="n">
         <v>0.625</v>
@@ -5450,25 +5450,25 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L88" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M88" t="n">
-        <v>0.913</v>
+        <v>0.9537</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0449</v>
+        <v>0.1458</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>274.1</v>
+        <v>639.2</v>
       </c>
       <c r="Q88" t="n">
         <v>4966</v>
@@ -5498,7 +5498,7 @@
         <v>0.9353</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9989</v>
+        <v>0.9962</v>
       </c>
       <c r="H89" t="n">
         <v>0.6875</v>
@@ -5507,25 +5507,25 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L89" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8883</v>
+        <v>0.9408</v>
       </c>
       <c r="N89" t="n">
-        <v>0.0341</v>
+        <v>0.1093</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>282.7</v>
+        <v>977</v>
       </c>
       <c r="Q89" t="n">
         <v>6437</v>
@@ -5555,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9981</v>
+        <v>0.9984</v>
       </c>
       <c r="H90" t="n">
         <v>0.1562</v>
@@ -5564,25 +5564,25 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L90" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8044</v>
+        <v>0.8993</v>
       </c>
       <c r="N90" t="n">
-        <v>0.0498</v>
+        <v>0.0467</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>282.7</v>
+        <v>238.7</v>
       </c>
       <c r="Q90" t="n">
         <v>4414</v>
@@ -5612,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9987</v>
+        <v>0.9996</v>
       </c>
       <c r="H91" t="n">
         <v>0.09370000000000001</v>
@@ -5621,25 +5621,25 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6065</v>
+        <v>0.3101</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1621</v>
+        <v>0.5715</v>
       </c>
       <c r="L91" t="n">
-        <v>0.2314</v>
+        <v>0.1183</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7901</v>
+        <v>0.8925</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0354</v>
+        <v>0.0072</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>265.1</v>
+        <v>79.3</v>
       </c>
       <c r="Q91" t="n">
         <v>5931</v>

--- a/results/q4_output/健康度评价.xlsx
+++ b/results/q4_output/健康度评价.xlsx
@@ -536,40 +536,40 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9956</v>
+        <v>0.9948</v>
       </c>
       <c r="H2" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1503</v>
+        <v>0.1024</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1424.9</v>
+        <v>1692</v>
       </c>
       <c r="Q2" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="3">
@@ -593,40 +593,40 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9951</v>
+        <v>0.9948</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1509</v>
+        <v>0.102</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1457.3</v>
+        <v>1548</v>
       </c>
       <c r="Q3" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="4">
@@ -650,40 +650,40 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9941</v>
+        <v>0.9953</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1744</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1637.4</v>
+        <v>1295.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="5">
@@ -700,44 +700,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9954</v>
+        <v>0.9959</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3125</v>
+        <v>0.8324</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1386</v>
+        <v>0.1229</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1635.6</v>
+        <v>1451.2</v>
       </c>
       <c r="Q5" t="n">
         <v>11954</v>
@@ -757,47 +757,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9931</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5625</v>
+        <v>0.7457</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1628</v>
+        <v>0.1534</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1231.2</v>
+        <v>1541.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="7">
@@ -824,37 +824,37 @@
         <v>0.9466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9978</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.9422</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1022</v>
+        <v>0.1273</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>672.1</v>
+        <v>1380.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="8">
@@ -871,7 +871,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -881,37 +881,37 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9976</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.625</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1013</v>
+        <v>0.118</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>443.9</v>
+        <v>644.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="9">
@@ -928,47 +928,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9973</v>
+        <v>0.9969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6875</v>
+        <v>0.1214</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0759</v>
+        <v>0.0804</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>678.5</v>
+        <v>779.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="10">
@@ -985,47 +985,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9989</v>
+        <v>0.9876</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1562</v>
+        <v>0.9422</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0324</v>
+        <v>0.3369</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>165.7</v>
+        <v>1888</v>
       </c>
       <c r="Q10" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1052,37 +1052,37 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9997</v>
+        <v>0.9961</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="N11" t="n">
-        <v>0.005</v>
+        <v>0.1021</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>55.1</v>
+        <v>792.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="12">
@@ -1106,40 +1106,40 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9952</v>
+        <v>0.9943</v>
       </c>
       <c r="H12" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9121</v>
+        <v>0.9417</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1653</v>
+        <v>0.1127</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1567.4</v>
+        <v>1861.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="13">
@@ -1163,40 +1163,40 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9946</v>
+        <v>0.9943</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9505</v>
+        <v>0.9332</v>
       </c>
       <c r="N13" t="n">
-        <v>0.166</v>
+        <v>0.1122</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1603</v>
+        <v>1702.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="14">
@@ -1220,40 +1220,40 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9935</v>
+        <v>0.9948</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7536</v>
+        <v>0.9463</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1918</v>
+        <v>0.1063</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1801.2</v>
+        <v>1424.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="15">
@@ -1270,44 +1270,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9949</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3125</v>
+        <v>0.8415</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7638</v>
+        <v>0.8647</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1524</v>
+        <v>0.1352</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1799.2</v>
+        <v>1596.3</v>
       </c>
       <c r="Q15" t="n">
         <v>11954</v>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.994</v>
+        <v>0.9925</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5625</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8228</v>
+        <v>0.9051</v>
       </c>
       <c r="N16" t="n">
-        <v>0.179</v>
+        <v>0.1688</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1354.3</v>
+        <v>1695.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="17">
@@ -1394,37 +1394,37 @@
         <v>0.9466</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9976</v>
+        <v>0.9951</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.9454</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7006</v>
+        <v>0.9617</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1125</v>
+        <v>0.14</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>739.3</v>
+        <v>1518.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="18">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1451,37 +1451,37 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9974</v>
+        <v>0.9962</v>
       </c>
       <c r="H18" t="n">
-        <v>0.625</v>
+        <v>0.5574</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9014</v>
+        <v>0.8285</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1114</v>
+        <v>0.1298</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>488.3</v>
+        <v>709.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="19">
@@ -1498,47 +1498,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9971</v>
+        <v>0.9966</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6875</v>
+        <v>0.1148</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8733</v>
+        <v>0.6585</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0835</v>
+        <v>0.0872</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>746.4</v>
+        <v>857.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="20">
@@ -1555,47 +1555,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9988</v>
+        <v>0.9863</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1562</v>
+        <v>0.9454</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7785</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0357</v>
+        <v>0.3706</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>182.3</v>
+        <v>2076.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="21">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1622,37 +1622,37 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9997</v>
+        <v>0.9957</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2936</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0495</v>
+        <v>0.3218</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2625</v>
+        <v>0.3846</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7621</v>
+        <v>0.614</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0055</v>
+        <v>0.1107</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>60.6</v>
+        <v>872.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="22">
@@ -1676,40 +1676,40 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9947</v>
+        <v>0.9937</v>
       </c>
       <c r="H22" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9121</v>
+        <v>0.9545</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1818</v>
+        <v>0.1239</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1724.2</v>
+        <v>2047.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="23">
@@ -1733,40 +1733,40 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9941</v>
+        <v>0.9937</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9505</v>
+        <v>0.9482</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1826</v>
+        <v>0.1234</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1763.3</v>
+        <v>1873.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="24">
@@ -1790,40 +1790,40 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9928</v>
+        <v>0.9943</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>0.211</v>
+        <v>0.1169</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1981.3</v>
+        <v>1567.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="25">
@@ -1840,44 +1840,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9944</v>
+        <v>0.995</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3125</v>
+        <v>0.8497</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7637</v>
+        <v>0.898</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1677</v>
+        <v>0.1487</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1979.1</v>
+        <v>1756</v>
       </c>
       <c r="Q25" t="n">
         <v>11954</v>
@@ -1897,47 +1897,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9917</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5625</v>
+        <v>0.772</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8228</v>
+        <v>0.9281</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1969</v>
+        <v>0.1857</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1489.7</v>
+        <v>1865.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="27">
@@ -1964,37 +1964,37 @@
         <v>0.9466</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9974</v>
+        <v>0.9946</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.9482</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7006</v>
+        <v>0.9702</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1237</v>
+        <v>0.154</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>813.2</v>
+        <v>1670.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="28">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2021,37 +2021,37 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9971</v>
+        <v>0.9958</v>
       </c>
       <c r="H28" t="n">
-        <v>0.625</v>
+        <v>0.5803</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9014</v>
+        <v>0.873</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1225</v>
+        <v>0.1428</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>537.1</v>
+        <v>780.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="29">
@@ -2068,47 +2068,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9968</v>
+        <v>0.9963</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6875</v>
+        <v>0.1088</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8733</v>
+        <v>0.7328</v>
       </c>
       <c r="N29" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>821</v>
+        <v>942.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>6437</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="30">
@@ -2125,47 +2125,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9987</v>
+        <v>0.9122</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1562</v>
+        <v>0.9482</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7784</v>
+        <v>0.892</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0393</v>
+        <v>0.4076</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>200.6</v>
+        <v>2284.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="31">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2192,37 +2192,37 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9997</v>
+        <v>0.9953</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2207</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0495</v>
+        <v>0.4815</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2625</v>
+        <v>0.2978</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7621</v>
+        <v>0.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.006</v>
+        <v>0.1199</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>66.59999999999999</v>
+        <v>959.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="32">
@@ -2246,40 +2246,40 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9956</v>
+        <v>0.9948</v>
       </c>
       <c r="H32" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1503</v>
+        <v>0.1024</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1424.9</v>
+        <v>1692</v>
       </c>
       <c r="Q32" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="33">
@@ -2303,40 +2303,40 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9951</v>
+        <v>0.9948</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1509</v>
+        <v>0.102</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1457.3</v>
+        <v>1548</v>
       </c>
       <c r="Q33" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="34">
@@ -2360,40 +2360,40 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9941</v>
+        <v>0.9953</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1744</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1637.4</v>
+        <v>1295.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="35">
@@ -2410,44 +2410,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9954</v>
+        <v>0.9959</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3125</v>
+        <v>0.8324</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1386</v>
+        <v>0.1229</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1635.6</v>
+        <v>1451.2</v>
       </c>
       <c r="Q35" t="n">
         <v>11954</v>
@@ -2467,47 +2467,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9931</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5625</v>
+        <v>0.7457</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1628</v>
+        <v>0.1534</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1231.2</v>
+        <v>1541.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="37">
@@ -2534,37 +2534,37 @@
         <v>0.9466</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9978</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.9422</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1022</v>
+        <v>0.1273</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>672.1</v>
+        <v>1380.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="38">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2591,37 +2591,37 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9976</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.625</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1013</v>
+        <v>0.118</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>443.9</v>
+        <v>644.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="39">
@@ -2638,47 +2638,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9973</v>
+        <v>0.9969</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6875</v>
+        <v>0.1214</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0759</v>
+        <v>0.0804</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>678.5</v>
+        <v>779.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="40">
@@ -2695,47 +2695,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9989</v>
+        <v>0.9876</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1562</v>
+        <v>0.9422</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0324</v>
+        <v>0.3369</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>165.7</v>
+        <v>1888</v>
       </c>
       <c r="Q40" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="41">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2762,37 +2762,37 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9997</v>
+        <v>0.9961</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="N41" t="n">
-        <v>0.005</v>
+        <v>0.1021</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>55.1</v>
+        <v>792.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="42">
@@ -2816,40 +2816,40 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G42" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="H42" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9121</v>
+        <v>0.9514</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1728</v>
+        <v>0.1178</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1638.7</v>
+        <v>1945.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="43">
@@ -2873,40 +2873,40 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9944</v>
+        <v>0.994</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9505</v>
+        <v>0.9445</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1736</v>
+        <v>0.1173</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1675.8</v>
+        <v>1780.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="44">
@@ -2930,40 +2930,40 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9932</v>
+        <v>0.9946</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7536</v>
+        <v>0.9553</v>
       </c>
       <c r="N44" t="n">
-        <v>0.2005</v>
+        <v>0.1111</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1883</v>
+        <v>1489.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="45">
@@ -2980,44 +2980,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9947</v>
+        <v>0.9953</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3125</v>
+        <v>0.8415</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7637</v>
+        <v>0.889</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1594</v>
+        <v>0.1414</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1881</v>
+        <v>1668.9</v>
       </c>
       <c r="Q45" t="n">
         <v>11954</v>
@@ -3037,47 +3037,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9937</v>
+        <v>0.9921</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5625</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8228</v>
+        <v>0.9212</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1872</v>
+        <v>0.1765</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1415.8</v>
+        <v>1772.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="47">
@@ -3104,37 +3104,37 @@
         <v>0.9466</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9948</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.9454</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7006</v>
+        <v>0.9678</v>
       </c>
       <c r="N47" t="n">
-        <v>0.1176</v>
+        <v>0.1464</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>772.9</v>
+        <v>1587.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="48">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3161,37 +3161,37 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9973</v>
+        <v>0.996</v>
       </c>
       <c r="H48" t="n">
-        <v>0.625</v>
+        <v>0.5574</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9014</v>
+        <v>0.8597</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1164</v>
+        <v>0.1357</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>510.5</v>
+        <v>741.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="49">
@@ -3208,47 +3208,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9969</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6875</v>
+        <v>0.1148</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8733</v>
+        <v>0.7214</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0873</v>
+        <v>0.0912</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>780.3</v>
+        <v>896.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="50">
@@ -3265,47 +3265,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9987</v>
+        <v>0.9661</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1562</v>
+        <v>0.9454</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7785</v>
+        <v>0.9133</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0373</v>
+        <v>0.3874</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>190.6</v>
+        <v>2171.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="51">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3332,37 +3332,37 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9997</v>
+        <v>0.9956</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2389</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0495</v>
+        <v>0.4482</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2625</v>
+        <v>0.3129</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7621</v>
+        <v>0.6851</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0057</v>
+        <v>0.1157</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>63.3</v>
+        <v>911.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="52">
@@ -3386,40 +3386,40 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9942</v>
+        <v>0.9344</v>
       </c>
       <c r="H52" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9486</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1987</v>
+        <v>0.1354</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>1884.5</v>
+        <v>2237.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="53">
@@ -3443,40 +3443,40 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9935</v>
+        <v>0.9931</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9696</v>
+        <v>0.9449</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1996</v>
+        <v>0.1349</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1927.2</v>
+        <v>2047.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="54">
@@ -3500,40 +3500,40 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9688</v>
+        <v>0.9938</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8487</v>
+        <v>0.9555</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2306</v>
+        <v>0.1278</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2165.5</v>
+        <v>1712.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="55">
@@ -3550,44 +3550,44 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9699</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3125</v>
+        <v>0.8497</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8548</v>
+        <v>0.8952</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1833</v>
+        <v>0.1626</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2163.1</v>
+        <v>1919.2</v>
       </c>
       <c r="Q55" t="n">
         <v>11954</v>
@@ -3607,47 +3607,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9928</v>
+        <v>0.9909</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5625</v>
+        <v>0.772</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K56" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8984</v>
+        <v>0.9291</v>
       </c>
       <c r="N56" t="n">
-        <v>0.2152</v>
+        <v>0.2029</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1628.2</v>
+        <v>2038.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="57">
@@ -3674,37 +3674,37 @@
         <v>0.9466</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9971</v>
+        <v>0.9941</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.9482</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8325</v>
+        <v>0.9695</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1352</v>
+        <v>0.1684</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>888.8</v>
+        <v>1826.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="58">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3731,37 +3731,37 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9968</v>
+        <v>0.9954</v>
       </c>
       <c r="H58" t="n">
-        <v>0.625</v>
+        <v>0.5803</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M58" t="n">
-        <v>0.9439</v>
+        <v>0.8752</v>
       </c>
       <c r="N58" t="n">
-        <v>0.1339</v>
+        <v>0.1561</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>587.1</v>
+        <v>852.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="59">
@@ -3778,47 +3778,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6875</v>
+        <v>0.1606</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9281</v>
+        <v>0.7527</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1003</v>
+        <v>0.1049</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>897.3</v>
+        <v>1030.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="60">
@@ -3835,44 +3835,44 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9986</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1562</v>
+        <v>0.8964</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8764</v>
+        <v>0.8269</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0429</v>
+        <v>0.4339</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>219.2</v>
+        <v>2496.9</v>
       </c>
       <c r="Q60" t="n">
         <v>4414</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3902,37 +3902,37 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9996</v>
+        <v>0.9949</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3819</v>
+        <v>0.2346</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1457</v>
+        <v>0.2923</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8678</v>
+        <v>0.7053</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0066</v>
+        <v>0.1311</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>72.8</v>
+        <v>1048.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="62">
@@ -3956,40 +3956,40 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9956</v>
+        <v>0.9948</v>
       </c>
       <c r="H62" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1503</v>
+        <v>0.1024</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1424.9</v>
+        <v>1692</v>
       </c>
       <c r="Q62" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="63">
@@ -4013,40 +4013,40 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9951</v>
+        <v>0.9948</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="N63" t="n">
-        <v>0.1509</v>
+        <v>0.102</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1457.3</v>
+        <v>1548</v>
       </c>
       <c r="Q63" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="64">
@@ -4070,40 +4070,40 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9941</v>
+        <v>0.9953</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1744</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1637.4</v>
+        <v>1295.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="65">
@@ -4120,44 +4120,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9954</v>
+        <v>0.9959</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3125</v>
+        <v>0.8324</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1386</v>
+        <v>0.1229</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1635.6</v>
+        <v>1451.2</v>
       </c>
       <c r="Q65" t="n">
         <v>11954</v>
@@ -4177,47 +4177,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9931</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5625</v>
+        <v>0.7457</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1628</v>
+        <v>0.1534</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1231.2</v>
+        <v>1541.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="67">
@@ -4244,37 +4244,37 @@
         <v>0.9466</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9978</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.9422</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1022</v>
+        <v>0.1273</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>672.1</v>
+        <v>1380.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="68">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -4301,37 +4301,37 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9976</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>0.625</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1013</v>
+        <v>0.118</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>443.9</v>
+        <v>644.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="69">
@@ -4348,47 +4348,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9973</v>
+        <v>0.9969</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6875</v>
+        <v>0.1214</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0759</v>
+        <v>0.0804</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>678.5</v>
+        <v>779.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="70">
@@ -4405,47 +4405,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9989</v>
+        <v>0.9876</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1562</v>
+        <v>0.9422</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0324</v>
+        <v>0.3369</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>165.7</v>
+        <v>1888</v>
       </c>
       <c r="Q70" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="71">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -4472,37 +4472,37 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9997</v>
+        <v>0.9961</v>
       </c>
       <c r="H71" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2973</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0495</v>
+        <v>0.3258</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2625</v>
+        <v>0.3768</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="N71" t="n">
-        <v>0.005</v>
+        <v>0.1021</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>55.1</v>
+        <v>792.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="72">
@@ -4526,40 +4526,40 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9947</v>
+        <v>0.9938</v>
       </c>
       <c r="H72" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9121</v>
+        <v>0.9539</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1803</v>
+        <v>0.1229</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1709.9</v>
+        <v>2030.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="73">
@@ -4583,40 +4583,40 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9941</v>
+        <v>0.9938</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9505</v>
+        <v>0.9475</v>
       </c>
       <c r="N73" t="n">
-        <v>0.1811</v>
+        <v>0.1224</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1748.7</v>
+        <v>1857.6</v>
       </c>
       <c r="Q73" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="74">
@@ -4640,40 +4640,40 @@
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9929</v>
+        <v>0.9944</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7536</v>
+        <v>0.9577</v>
       </c>
       <c r="N74" t="n">
-        <v>0.2092</v>
+        <v>0.1159</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1964.9</v>
+        <v>1554.2</v>
       </c>
       <c r="Q74" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="75">
@@ -4690,44 +4690,44 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9944</v>
+        <v>0.9951</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3125</v>
+        <v>0.8415</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7637</v>
+        <v>0.8956</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1663</v>
+        <v>0.1475</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1962.7</v>
+        <v>1741.4</v>
       </c>
       <c r="Q75" t="n">
         <v>11954</v>
@@ -4747,47 +4747,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9918</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5625</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8228</v>
+        <v>0.9256</v>
       </c>
       <c r="N76" t="n">
-        <v>0.1953</v>
+        <v>0.1841</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1477.4</v>
+        <v>1849.9</v>
       </c>
       <c r="Q76" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="77">
@@ -4814,37 +4814,37 @@
         <v>0.9466</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9974</v>
+        <v>0.9946</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.9454</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7006</v>
+        <v>0.9694</v>
       </c>
       <c r="N77" t="n">
-        <v>0.1227</v>
+        <v>0.1528</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>806.5</v>
+        <v>1657</v>
       </c>
       <c r="Q77" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="78">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -4871,37 +4871,37 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9971</v>
+        <v>0.9958</v>
       </c>
       <c r="H78" t="n">
-        <v>0.625</v>
+        <v>0.5574</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M78" t="n">
-        <v>0.9014</v>
+        <v>0.8683</v>
       </c>
       <c r="N78" t="n">
-        <v>0.1215</v>
+        <v>0.1416</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>532.7</v>
+        <v>773.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="79">
@@ -4918,47 +4918,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9968</v>
+        <v>0.9963</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6875</v>
+        <v>0.1148</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8733</v>
+        <v>0.7389</v>
       </c>
       <c r="N79" t="n">
-        <v>0.091</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>814.2</v>
+        <v>935</v>
       </c>
       <c r="Q79" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="80">
@@ -4975,47 +4975,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9987</v>
+        <v>0.9211</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1562</v>
+        <v>0.9454</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7784</v>
+        <v>0.895</v>
       </c>
       <c r="N80" t="n">
-        <v>0.0389</v>
+        <v>0.4043</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>198.9</v>
+        <v>2265.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="81">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -5042,37 +5042,37 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9997</v>
+        <v>0.9954</v>
       </c>
       <c r="H81" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.2237</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0495</v>
+        <v>0.4834</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2625</v>
+        <v>0.293</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7621</v>
+        <v>0.7048</v>
       </c>
       <c r="N81" t="n">
-        <v>0.006</v>
+        <v>0.1207</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>66.09999999999999</v>
+        <v>951.4</v>
       </c>
       <c r="Q81" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="82">
@@ -5096,40 +5096,40 @@
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9203</v>
+        <v>0.8076</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9937</v>
+        <v>0.8398</v>
       </c>
       <c r="H82" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9569</v>
+        <v>0.883</v>
       </c>
       <c r="N82" t="n">
-        <v>0.2164</v>
+        <v>0.1475</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>2051.9</v>
+        <v>2436.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
     </row>
     <row r="83">
@@ -5153,40 +5153,40 @@
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="G83" t="n">
-        <v>0.993</v>
+        <v>0.9385</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M83" t="n">
-        <v>0.9738</v>
+        <v>0.9171</v>
       </c>
       <c r="N83" t="n">
-        <v>0.2173</v>
+        <v>0.1469</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>2098.5</v>
+        <v>2229.1</v>
       </c>
       <c r="Q83" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="84">
@@ -5210,40 +5210,40 @@
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0.8229</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8772</v>
+        <v>0.9932</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L84" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M84" t="n">
-        <v>0.8189</v>
+        <v>0.9515</v>
       </c>
       <c r="N84" t="n">
-        <v>0.2511</v>
+        <v>0.1391</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2357.9</v>
+        <v>1865.1</v>
       </c>
       <c r="Q84" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="85">
@@ -5260,44 +5260,44 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9193</v>
+        <v>0.7516</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8784</v>
+        <v>0.9941</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3125</v>
+        <v>0.8497</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L85" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M85" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8852</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1996</v>
+        <v>0.177</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2355.3</v>
+        <v>2089.7</v>
       </c>
       <c r="Q85" t="n">
         <v>11954</v>
@@ -5317,47 +5317,47 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9098000000000001</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9921</v>
+        <v>0.9429</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5625</v>
+        <v>0.772</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M86" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2344</v>
+        <v>0.221</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>1772.9</v>
+        <v>2219.9</v>
       </c>
       <c r="Q86" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
     </row>
     <row r="87">
@@ -5384,37 +5384,37 @@
         <v>0.9466</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9969</v>
+        <v>0.9935</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>0.9482</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L87" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M87" t="n">
-        <v>0.8633</v>
+        <v>0.9669</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1472</v>
+        <v>0.1833</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>967.8</v>
+        <v>1988.4</v>
       </c>
       <c r="Q87" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
     </row>
     <row r="88">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -5441,37 +5441,37 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9966</v>
+        <v>0.995</v>
       </c>
       <c r="H88" t="n">
-        <v>0.625</v>
+        <v>0.5803</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9537</v>
+        <v>0.863</v>
       </c>
       <c r="N88" t="n">
-        <v>0.1458</v>
+        <v>0.1699</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>639.2</v>
+        <v>928.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="89">
@@ -5488,47 +5488,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9962</v>
+        <v>0.9956</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6875</v>
+        <v>0.1606</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M89" t="n">
-        <v>0.9408</v>
+        <v>0.7284</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1093</v>
+        <v>0.1142</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>977</v>
+        <v>1122</v>
       </c>
       <c r="Q89" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="90">
@@ -5545,44 +5545,44 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0.7724</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9984</v>
+        <v>0.7054</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1562</v>
+        <v>0.8964</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L90" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8993</v>
+        <v>0.784</v>
       </c>
       <c r="N90" t="n">
-        <v>0.0467</v>
+        <v>0.4725</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>238.7</v>
+        <v>2718.7</v>
       </c>
       <c r="Q90" t="n">
         <v>4414</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -5612,37 +5612,37 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9996</v>
+        <v>0.9944</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09370000000000001</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.3101</v>
+        <v>0.2579</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5715</v>
+        <v>0.4208</v>
       </c>
       <c r="L91" t="n">
-        <v>0.1183</v>
+        <v>0.3214</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8925</v>
+        <v>0.6763</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0072</v>
+        <v>0.1427</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>79.3</v>
+        <v>1141.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
     </row>
   </sheetData>
